--- a/AAII_Financials/Yearly/SWRAY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/SWRAY_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="92">
   <si>
     <t>SWRAY</t>
   </si>
@@ -305,7 +305,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yy;@"/>
+    <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -347,7 +347,7 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -656,135 +656,159 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:K102"/>
+  <dimension ref="A5:M102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>43830</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>43465</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>43100</v>
       </c>
-      <c r="K7" s="2"/>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="M7" s="2"/>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>11623000</v>
+      </c>
+      <c r="E8" s="3">
+        <v>10552800</v>
+      </c>
+      <c r="F8" s="3">
         <v>12138400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>11692400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>11699400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>10106100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>10996400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>10803500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>10275700</v>
       </c>
-      <c r="K8" s="3"/>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="M8" s="3"/>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>7288300</v>
+      </c>
+      <c r="E9" s="3">
+        <v>6631000</v>
+      </c>
+      <c r="F9" s="3">
         <v>7638900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>7307800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>7175900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>6172700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>6911100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>6862100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>6654000</v>
       </c>
-      <c r="K9" s="3"/>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="M9" s="3"/>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>4334700</v>
+      </c>
+      <c r="E10" s="3">
+        <v>3921900</v>
+      </c>
+      <c r="F10" s="3">
         <v>4499400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>4384600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>4523500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>3933400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>4085300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>3941500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>3621700</v>
       </c>
-      <c r="K10" s="3"/>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="M10" s="3"/>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -796,8 +820,10 @@
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L11" s="3"/>
+      <c r="M11" s="3"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -822,9 +848,15 @@
       <c r="J12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K12" s="3"/>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M12" s="3"/>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -849,63 +881,81 @@
       <c r="J13" s="3">
         <v>0</v>
       </c>
-      <c r="K13" s="3"/>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K13" s="3">
+        <v>0</v>
+      </c>
+      <c r="L13" s="3">
+        <v>0</v>
+      </c>
+      <c r="M13" s="3"/>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>861700</v>
+      </c>
+      <c r="E14" s="3">
+        <v>787800</v>
+      </c>
+      <c r="F14" s="3">
         <v>-2470200</v>
       </c>
-      <c r="E14" s="3">
+      <c r="G14" s="3">
         <v>-99300</v>
       </c>
-      <c r="F14" s="3">
+      <c r="H14" s="3">
         <v>18500</v>
       </c>
-      <c r="G14" s="3">
+      <c r="I14" s="3">
         <v>381900</v>
       </c>
-      <c r="H14" s="3">
+      <c r="J14" s="3">
         <v>-416100</v>
       </c>
-      <c r="I14" s="3">
+      <c r="K14" s="3">
         <v>-2572600</v>
       </c>
-      <c r="J14" s="3">
+      <c r="L14" s="3">
         <v>-3221500</v>
       </c>
-      <c r="K14" s="3"/>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="M14" s="3"/>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>412900</v>
+      </c>
+      <c r="E15" s="3">
+        <v>351900</v>
+      </c>
+      <c r="F15" s="3">
         <v>399000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="G15" s="3">
         <v>360400</v>
       </c>
-      <c r="F15" s="3">
+      <c r="H15" s="3">
         <v>385200</v>
       </c>
-      <c r="G15" s="3">
+      <c r="I15" s="3">
         <v>400300</v>
       </c>
-      <c r="H15" s="3">
+      <c r="J15" s="3">
         <v>465300</v>
       </c>
-      <c r="I15" s="3">
+      <c r="K15" s="3">
         <v>471100</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>444900</v>
       </c>
-      <c r="K15" s="3"/>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="M15" s="3"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -914,62 +964,76 @@
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
-    </row>
-    <row r="17" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L16" s="3"/>
+      <c r="M16" s="3"/>
+    </row>
+    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>10168300</v>
+      </c>
+      <c r="E17" s="3">
+        <v>9251800</v>
+      </c>
+      <c r="F17" s="3">
         <v>10655400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>10282900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>10130000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>8727900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>9642700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>9439600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>8919400</v>
       </c>
-      <c r="K17" s="3"/>
-    </row>
-    <row r="18" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="M17" s="3"/>
+    </row>
+    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>1454800</v>
+      </c>
+      <c r="E18" s="3">
+        <v>1301100</v>
+      </c>
+      <c r="F18" s="3">
         <v>1483000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>1409500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>1569400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>1378200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>1353700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>1363900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>1356400</v>
       </c>
-      <c r="K18" s="3"/>
-    </row>
-    <row r="19" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="M18" s="3"/>
+    </row>
+    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -981,143 +1045,175 @@
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
-    </row>
-    <row r="20" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L19" s="3"/>
+      <c r="M19" s="3"/>
+    </row>
+    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-478900</v>
+        <v>-457600</v>
       </c>
       <c r="E20" s="3">
+        <v>-778200</v>
+      </c>
+      <c r="F20" s="3">
+        <v>-485400</v>
+      </c>
+      <c r="G20" s="3">
         <v>200100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>98200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>1110900</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>-348900</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>-472100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>-228500</v>
       </c>
-      <c r="K20" s="3"/>
-    </row>
-    <row r="21" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="M20" s="3"/>
+    </row>
+    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>2360900</v>
+        <v>2325300</v>
       </c>
       <c r="E21" s="3">
+        <v>2431200</v>
+      </c>
+      <c r="F21" s="3">
+        <v>2367400</v>
+      </c>
+      <c r="G21" s="3">
         <v>1569800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>1856400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>667700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>2167900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>2307000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>2029700</v>
       </c>
-      <c r="K21" s="3"/>
-    </row>
-    <row r="22" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="M21" s="3"/>
+    </row>
+    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>312300</v>
+        <v>362100</v>
       </c>
       <c r="E22" s="3">
+        <v>346700</v>
+      </c>
+      <c r="F22" s="3">
+        <v>304800</v>
+      </c>
+      <c r="G22" s="3">
         <v>202100</v>
       </c>
-      <c r="F22" s="3">
+      <c r="H22" s="3">
         <v>237500</v>
       </c>
-      <c r="G22" s="3">
+      <c r="I22" s="3">
         <v>274600</v>
       </c>
-      <c r="H22" s="3">
+      <c r="J22" s="3">
         <v>304800</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>304900</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>283000</v>
       </c>
-      <c r="K22" s="3"/>
-    </row>
-    <row r="23" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="M22" s="3"/>
+    </row>
+    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>749800</v>
+      </c>
+      <c r="E23" s="3">
+        <v>1002300</v>
+      </c>
+      <c r="F23" s="3">
         <v>4194900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>1143700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>1256000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-341000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>1872400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>4130300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>4544200</v>
       </c>
-      <c r="K23" s="3"/>
-    </row>
-    <row r="24" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="M23" s="3"/>
+    </row>
+    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>300800</v>
+      </c>
+      <c r="E24" s="3">
+        <v>397000</v>
+      </c>
+      <c r="F24" s="3">
         <v>375300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>386400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>393700</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>312800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>352500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>373600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>399800</v>
       </c>
-      <c r="K24" s="3"/>
-    </row>
-    <row r="25" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="M24" s="3"/>
+    </row>
+    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1142,63 +1238,81 @@
       <c r="J25" s="3">
         <v>0</v>
       </c>
-      <c r="K25" s="3"/>
-    </row>
-    <row r="26" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K25" s="3">
+        <v>0</v>
+      </c>
+      <c r="L25" s="3">
+        <v>0</v>
+      </c>
+      <c r="M25" s="3"/>
+    </row>
+    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>449000</v>
+      </c>
+      <c r="E26" s="3">
+        <v>605200</v>
+      </c>
+      <c r="F26" s="3">
         <v>3819600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>757300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>862300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-653800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>1519800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>3756700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>4144400</v>
       </c>
-      <c r="K26" s="3"/>
-    </row>
-    <row r="27" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="M26" s="3"/>
+    </row>
+    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>377500</v>
+      </c>
+      <c r="E27" s="3">
+        <v>556300</v>
+      </c>
+      <c r="F27" s="3">
         <v>3693500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>538000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>430500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-1418600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>1156400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>3017200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>3336600</v>
       </c>
-      <c r="K27" s="3"/>
-    </row>
-    <row r="28" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="M27" s="3"/>
+    </row>
+    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1223,9 +1337,15 @@
       <c r="J28" s="3">
         <v>0</v>
       </c>
-      <c r="K28" s="3"/>
-    </row>
-    <row r="29" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K28" s="3">
+        <v>0</v>
+      </c>
+      <c r="L28" s="3">
+        <v>0</v>
+      </c>
+      <c r="M28" s="3"/>
+    </row>
+    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1233,26 +1353,32 @@
         <v>0</v>
       </c>
       <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3">
         <v>46000</v>
       </c>
-      <c r="F29" s="3">
+      <c r="H29" s="3">
         <v>-205100</v>
       </c>
-      <c r="G29" s="3">
+      <c r="I29" s="3">
         <v>-645700</v>
       </c>
-      <c r="H29" s="3">
-        <v>0</v>
-      </c>
-      <c r="I29" s="3">
-        <v>0</v>
-      </c>
       <c r="J29" s="3">
         <v>0</v>
       </c>
-      <c r="K29" s="3"/>
-    </row>
-    <row r="30" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K29" s="3">
+        <v>0</v>
+      </c>
+      <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3"/>
+    </row>
+    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1277,9 +1403,15 @@
       <c r="J30" s="3">
         <v>0</v>
       </c>
-      <c r="K30" s="3"/>
-    </row>
-    <row r="31" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K30" s="3">
+        <v>0</v>
+      </c>
+      <c r="L30" s="3">
+        <v>0</v>
+      </c>
+      <c r="M30" s="3"/>
+    </row>
+    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1304,63 +1436,81 @@
       <c r="J31" s="3">
         <v>0</v>
       </c>
-      <c r="K31" s="3"/>
-    </row>
-    <row r="32" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K31" s="3">
+        <v>0</v>
+      </c>
+      <c r="L31" s="3">
+        <v>0</v>
+      </c>
+      <c r="M31" s="3"/>
+    </row>
+    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>478900</v>
+        <v>457600</v>
       </c>
       <c r="E32" s="3">
+        <v>778200</v>
+      </c>
+      <c r="F32" s="3">
+        <v>485400</v>
+      </c>
+      <c r="G32" s="3">
         <v>-200100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>-98200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>-1110900</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>348900</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>472100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>228500</v>
       </c>
-      <c r="K32" s="3"/>
-    </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="M32" s="3"/>
+    </row>
+    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>377500</v>
+      </c>
+      <c r="E33" s="3">
+        <v>556300</v>
+      </c>
+      <c r="F33" s="3">
         <v>3693500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>538000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>430500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-1418600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>1156400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>3017200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>3336600</v>
       </c>
-      <c r="K33" s="3"/>
-    </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="M33" s="3"/>
+    </row>
+    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1385,68 +1535,86 @@
       <c r="J34" s="3">
         <v>0</v>
       </c>
-      <c r="K34" s="3"/>
-    </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K34" s="3">
+        <v>0</v>
+      </c>
+      <c r="L34" s="3">
+        <v>0</v>
+      </c>
+      <c r="M34" s="3"/>
+    </row>
+    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>377500</v>
+      </c>
+      <c r="E35" s="3">
+        <v>556300</v>
+      </c>
+      <c r="F35" s="3">
         <v>3693500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>538000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>430500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-1418600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>1156400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>3017200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>3336600</v>
       </c>
-      <c r="K35" s="3"/>
-    </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="M35" s="3"/>
+    </row>
+    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>43830</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>43465</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>43100</v>
       </c>
-      <c r="K38" s="2"/>
-    </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="M38" s="2"/>
+    </row>
+    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1458,8 +1626,10 @@
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
-    </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L39" s="3"/>
+      <c r="M39" s="3"/>
+    </row>
+    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1471,251 +1641,307 @@
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
-    </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L40" s="3"/>
+      <c r="M40" s="3"/>
+    </row>
+    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2693700</v>
+      </c>
+      <c r="E41" s="3">
+        <v>2540100</v>
+      </c>
+      <c r="F41" s="3">
         <v>1514500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>1379700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>2856700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>3770400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>2737400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>1162300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>761600</v>
       </c>
-      <c r="K41" s="3"/>
-    </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="M41" s="3"/>
+    </row>
+    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>283400</v>
+      </c>
+      <c r="E42" s="3">
+        <v>167100</v>
+      </c>
+      <c r="F42" s="3">
         <v>288200</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>109800</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>79300</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>4000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>3000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>1300</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>15500</v>
       </c>
-      <c r="K42" s="3"/>
-    </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="M42" s="3"/>
+    </row>
+    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1299600</v>
+      </c>
+      <c r="E43" s="3">
+        <v>1321000</v>
+      </c>
+      <c r="F43" s="3">
         <v>1015000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>1148900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>982600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>1086400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>1039500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>1162900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>1143200</v>
       </c>
-      <c r="K43" s="3"/>
-    </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="M43" s="3"/>
+    </row>
+    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>3071000</v>
+      </c>
+      <c r="E44" s="3">
+        <v>2655200</v>
+      </c>
+      <c r="F44" s="3">
         <v>2031300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>2035600</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>1551200</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>1115700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>1173800</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>856900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>1091600</v>
       </c>
-      <c r="K44" s="3"/>
-    </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="M44" s="3"/>
+    </row>
+    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>7800</v>
+      </c>
+      <c r="E45" s="3">
+        <v>648200</v>
+      </c>
+      <c r="F45" s="3">
         <v>72100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>265900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>465400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>59700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>5900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>1996500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>808500</v>
       </c>
-      <c r="K45" s="3"/>
-    </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="M45" s="3"/>
+    </row>
+    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>7700700</v>
+      </c>
+      <c r="E46" s="3">
+        <v>7645400</v>
+      </c>
+      <c r="F46" s="3">
         <v>5208000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>5224800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>6193600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>6328800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>5193500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>5437000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>4082300</v>
       </c>
-      <c r="K46" s="3"/>
-    </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="M46" s="3"/>
+    </row>
+    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>8568400</v>
+      </c>
+      <c r="E47" s="3">
+        <v>8319300</v>
+      </c>
+      <c r="F47" s="3">
         <v>7841000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>7063100</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>7323800</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>6619500</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>6419200</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>6467200</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>5820200</v>
       </c>
-      <c r="K47" s="3"/>
-    </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="M47" s="3"/>
+    </row>
+    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>4387500</v>
+      </c>
+      <c r="E48" s="3">
+        <v>4190700</v>
+      </c>
+      <c r="F48" s="3">
         <v>3784600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>3887600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>3990500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>4501700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>5466500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>5062200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>5838500</v>
       </c>
-      <c r="K48" s="3"/>
-    </row>
-    <row r="49" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="M48" s="3"/>
+    </row>
+    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>4125900</v>
+      </c>
+      <c r="E49" s="3">
+        <v>4012400</v>
+      </c>
+      <c r="F49" s="3">
         <v>2309400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>1786500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>1717800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>1689100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>1650000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>1649500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>1726000</v>
       </c>
-      <c r="K49" s="3"/>
-    </row>
-    <row r="50" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="M49" s="3"/>
+    </row>
+    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1740,9 +1966,15 @@
       <c r="J50" s="3">
         <v>0</v>
       </c>
-      <c r="K50" s="3"/>
-    </row>
-    <row r="51" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K50" s="3">
+        <v>0</v>
+      </c>
+      <c r="L50" s="3">
+        <v>0</v>
+      </c>
+      <c r="M50" s="3"/>
+    </row>
+    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1767,36 +1999,48 @@
       <c r="J51" s="3">
         <v>0</v>
       </c>
-      <c r="K51" s="3"/>
-    </row>
-    <row r="52" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K51" s="3">
+        <v>0</v>
+      </c>
+      <c r="L51" s="3">
+        <v>0</v>
+      </c>
+      <c r="M51" s="3"/>
+    </row>
+    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>34508900</v>
+      </c>
+      <c r="E52" s="3">
+        <v>35074100</v>
+      </c>
+      <c r="F52" s="3">
         <v>36157500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>35761400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>34565100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>34625300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>35687500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>35050100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>34461900</v>
       </c>
-      <c r="K52" s="3"/>
-    </row>
-    <row r="53" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="M52" s="3"/>
+    </row>
+    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -1821,36 +2065,48 @@
       <c r="J53" s="3">
         <v>0</v>
       </c>
-      <c r="K53" s="3"/>
-    </row>
-    <row r="54" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K53" s="3">
+        <v>0</v>
+      </c>
+      <c r="L53" s="3">
+        <v>0</v>
+      </c>
+      <c r="M53" s="3"/>
+    </row>
+    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>61208500</v>
+      </c>
+      <c r="E54" s="3">
+        <v>61353200</v>
+      </c>
+      <c r="F54" s="3">
         <v>57317000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>55758500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>55871000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>55861200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>56668500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>55725500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>53894100</v>
       </c>
-      <c r="K54" s="3"/>
-    </row>
-    <row r="55" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="M54" s="3"/>
+    </row>
+    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -1862,8 +2118,10 @@
       <c r="I55" s="3"/>
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
-    </row>
-    <row r="56" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L55" s="3"/>
+      <c r="M55" s="3"/>
+    </row>
+    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -1875,170 +2133,208 @@
       <c r="I56" s="3"/>
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
-    </row>
-    <row r="57" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L56" s="3"/>
+      <c r="M56" s="3"/>
+    </row>
+    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>824100</v>
+      </c>
+      <c r="E57" s="3">
+        <v>862100</v>
+      </c>
+      <c r="F57" s="3">
         <v>770600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>843500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>743300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>610100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>610300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>550100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>607000</v>
       </c>
-      <c r="K57" s="3"/>
-    </row>
-    <row r="58" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="M57" s="3"/>
+    </row>
+    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2933000</v>
+      </c>
+      <c r="E58" s="3">
+        <v>2515700</v>
+      </c>
+      <c r="F58" s="3">
         <v>1546000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>1548200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>2497900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>1106200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>1639700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>1516200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>1287100</v>
       </c>
-      <c r="K58" s="3"/>
-    </row>
-    <row r="59" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="M58" s="3"/>
+    </row>
+    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>3003700</v>
+      </c>
+      <c r="E59" s="3">
+        <v>2709200</v>
+      </c>
+      <c r="F59" s="3">
         <v>2052800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>1784600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>1772600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>1497900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>1499100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>1735100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>1373800</v>
       </c>
-      <c r="K59" s="3"/>
-    </row>
-    <row r="60" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="M59" s="3"/>
+    </row>
+    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>7868900</v>
+      </c>
+      <c r="E60" s="3">
+        <v>7212900</v>
+      </c>
+      <c r="F60" s="3">
         <v>5352600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>5326500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>6191000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>4440200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>4822400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>4844500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>4157700</v>
       </c>
-      <c r="K60" s="3"/>
-    </row>
-    <row r="61" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="M60" s="3"/>
+    </row>
+    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>9694700</v>
+      </c>
+      <c r="E61" s="3">
+        <v>10290800</v>
+      </c>
+      <c r="F61" s="3">
         <v>8041500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>7986000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>6255000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>8460100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>7829000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>7693600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>8853200</v>
       </c>
-      <c r="K61" s="3"/>
-    </row>
-    <row r="62" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="M61" s="3"/>
+    </row>
+    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>292300</v>
+      </c>
+      <c r="E62" s="3">
+        <v>230600</v>
+      </c>
+      <c r="F62" s="3">
         <v>200200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>202200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>197400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>167300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>152400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>236100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>311300</v>
       </c>
-      <c r="K62" s="3"/>
-    </row>
-    <row r="63" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="M62" s="3"/>
+    </row>
+    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2063,9 +2359,15 @@
       <c r="J63" s="3">
         <v>0</v>
       </c>
-      <c r="K63" s="3"/>
-    </row>
-    <row r="64" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K63" s="3">
+        <v>0</v>
+      </c>
+      <c r="L63" s="3">
+        <v>0</v>
+      </c>
+      <c r="M63" s="3"/>
+    </row>
+    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2090,9 +2392,15 @@
       <c r="J64" s="3">
         <v>0</v>
       </c>
-      <c r="K64" s="3"/>
-    </row>
-    <row r="65" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K64" s="3">
+        <v>0</v>
+      </c>
+      <c r="L64" s="3">
+        <v>0</v>
+      </c>
+      <c r="M64" s="3"/>
+    </row>
+    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2117,36 +2425,48 @@
       <c r="J65" s="3">
         <v>0</v>
       </c>
-      <c r="K65" s="3"/>
-    </row>
-    <row r="66" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K65" s="3">
+        <v>0</v>
+      </c>
+      <c r="L65" s="3">
+        <v>0</v>
+      </c>
+      <c r="M65" s="3"/>
+    </row>
+    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>20579300</v>
+      </c>
+      <c r="E66" s="3">
+        <v>20327500</v>
+      </c>
+      <c r="F66" s="3">
         <v>15742500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>15239900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>14369200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>14698700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>14366600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>14210900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>14718900</v>
       </c>
-      <c r="K66" s="3"/>
-    </row>
-    <row r="67" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="M66" s="3"/>
+    </row>
+    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2158,8 +2478,10 @@
       <c r="I67" s="3"/>
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
-    </row>
-    <row r="68" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L67" s="3"/>
+      <c r="M67" s="3"/>
+    </row>
+    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2184,9 +2506,15 @@
       <c r="J68" s="3">
         <v>0</v>
       </c>
-      <c r="K68" s="3"/>
-    </row>
-    <row r="69" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K68" s="3">
+        <v>0</v>
+      </c>
+      <c r="L68" s="3">
+        <v>0</v>
+      </c>
+      <c r="M68" s="3"/>
+    </row>
+    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2211,9 +2539,15 @@
       <c r="J69" s="3">
         <v>0</v>
       </c>
-      <c r="K69" s="3"/>
-    </row>
-    <row r="70" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K69" s="3">
+        <v>0</v>
+      </c>
+      <c r="L69" s="3">
+        <v>0</v>
+      </c>
+      <c r="M69" s="3"/>
+    </row>
+    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2238,9 +2572,15 @@
       <c r="J70" s="3">
         <v>0</v>
       </c>
-      <c r="K70" s="3"/>
-    </row>
-    <row r="71" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K70" s="3">
+        <v>0</v>
+      </c>
+      <c r="L70" s="3">
+        <v>0</v>
+      </c>
+      <c r="M70" s="3"/>
+    </row>
+    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2265,36 +2605,48 @@
       <c r="J71" s="3">
         <v>0</v>
       </c>
-      <c r="K71" s="3"/>
-    </row>
-    <row r="72" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K71" s="3">
+        <v>0</v>
+      </c>
+      <c r="L71" s="3">
+        <v>0</v>
+      </c>
+      <c r="M71" s="3"/>
+    </row>
+    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>33269400</v>
+      </c>
+      <c r="E72" s="3">
+        <v>33562400</v>
+      </c>
+      <c r="F72" s="3">
         <v>34162800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>32725000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>32924700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>33070200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>34706100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>34073700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>31596900</v>
       </c>
-      <c r="K72" s="3"/>
-    </row>
-    <row r="73" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="M72" s="3"/>
+    </row>
+    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2319,9 +2671,15 @@
       <c r="J73" s="3">
         <v>0</v>
       </c>
-      <c r="K73" s="3"/>
-    </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K73" s="3">
+        <v>0</v>
+      </c>
+      <c r="L73" s="3">
+        <v>0</v>
+      </c>
+      <c r="M73" s="3"/>
+    </row>
+    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2346,9 +2704,15 @@
       <c r="J74" s="3">
         <v>0</v>
       </c>
-      <c r="K74" s="3"/>
-    </row>
-    <row r="75" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K74" s="3">
+        <v>0</v>
+      </c>
+      <c r="L74" s="3">
+        <v>0</v>
+      </c>
+      <c r="M74" s="3"/>
+    </row>
+    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2373,36 +2737,48 @@
       <c r="J75" s="3">
         <v>0</v>
       </c>
-      <c r="K75" s="3"/>
-    </row>
-    <row r="76" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K75" s="3">
+        <v>0</v>
+      </c>
+      <c r="L75" s="3">
+        <v>0</v>
+      </c>
+      <c r="M75" s="3"/>
+    </row>
+    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>33349900</v>
+      </c>
+      <c r="E76" s="3">
+        <v>33253900</v>
+      </c>
+      <c r="F76" s="3">
         <v>34323400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>33146900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>34178500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>33881200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>35094100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>34531000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>32400900</v>
       </c>
-      <c r="K76" s="3"/>
-    </row>
-    <row r="77" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="M76" s="3"/>
+    </row>
+    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2427,68 +2803,86 @@
       <c r="J77" s="3">
         <v>0</v>
       </c>
-      <c r="K77" s="3"/>
-    </row>
-    <row r="79" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K77" s="3">
+        <v>0</v>
+      </c>
+      <c r="L77" s="3">
+        <v>0</v>
+      </c>
+      <c r="M77" s="3"/>
+    </row>
+    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>43830</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>43465</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>43100</v>
       </c>
-      <c r="K80" s="2"/>
-    </row>
-    <row r="81" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="M80" s="2"/>
+    </row>
+    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>377500</v>
+      </c>
+      <c r="E81" s="3">
+        <v>556300</v>
+      </c>
+      <c r="F81" s="3">
         <v>3693500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>538000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>430500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-1418600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>1156400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>3017200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>3336600</v>
       </c>
-      <c r="K81" s="3"/>
-    </row>
-    <row r="82" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="M81" s="3"/>
+    </row>
+    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2500,35 +2894,43 @@
       <c r="I82" s="3"/>
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
-    </row>
-    <row r="83" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L82" s="3"/>
+      <c r="M82" s="3"/>
+    </row>
+    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>553600</v>
+      </c>
+      <c r="E83" s="3">
+        <v>474200</v>
+      </c>
+      <c r="F83" s="3">
         <v>509100</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>460400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>484900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>502500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>586200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>455700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>431400</v>
       </c>
-      <c r="K83" s="3"/>
-    </row>
-    <row r="84" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="M83" s="3"/>
+    </row>
+    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2553,9 +2955,15 @@
       <c r="J84" s="3">
         <v>0</v>
       </c>
-      <c r="K84" s="3"/>
-    </row>
-    <row r="85" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K84" s="3">
+        <v>0</v>
+      </c>
+      <c r="L84" s="3">
+        <v>0</v>
+      </c>
+      <c r="M84" s="3"/>
+    </row>
+    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2580,9 +2988,15 @@
       <c r="J85" s="3">
         <v>0</v>
       </c>
-      <c r="K85" s="3"/>
-    </row>
-    <row r="86" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K85" s="3">
+        <v>0</v>
+      </c>
+      <c r="L85" s="3">
+        <v>0</v>
+      </c>
+      <c r="M85" s="3"/>
+    </row>
+    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2607,9 +3021,15 @@
       <c r="J86" s="3">
         <v>0</v>
       </c>
-      <c r="K86" s="3"/>
-    </row>
-    <row r="87" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K86" s="3">
+        <v>0</v>
+      </c>
+      <c r="L86" s="3">
+        <v>0</v>
+      </c>
+      <c r="M86" s="3"/>
+    </row>
+    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2634,9 +3054,15 @@
       <c r="J87" s="3">
         <v>0</v>
       </c>
-      <c r="K87" s="3"/>
-    </row>
-    <row r="88" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K87" s="3">
+        <v>0</v>
+      </c>
+      <c r="L87" s="3">
+        <v>0</v>
+      </c>
+      <c r="M87" s="3"/>
+    </row>
+    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -2661,36 +3087,48 @@
       <c r="J88" s="3">
         <v>0</v>
       </c>
-      <c r="K88" s="3"/>
-    </row>
-    <row r="89" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K88" s="3">
+        <v>0</v>
+      </c>
+      <c r="L88" s="3">
+        <v>0</v>
+      </c>
+      <c r="M88" s="3"/>
+    </row>
+    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1869500</v>
+      </c>
+      <c r="E89" s="3">
+        <v>1346400</v>
+      </c>
+      <c r="F89" s="3">
         <v>1269500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>1046000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>1495900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>1477900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>1353300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>1971100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>1996600</v>
       </c>
-      <c r="K89" s="3"/>
-    </row>
-    <row r="90" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="M89" s="3"/>
+    </row>
+    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -2702,35 +3140,43 @@
       <c r="I90" s="3"/>
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
-    </row>
-    <row r="91" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L90" s="3"/>
+      <c r="M90" s="3"/>
+    </row>
+    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-707800</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-543500</v>
+      </c>
+      <c r="F91" s="3">
         <v>-428100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-399400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-488900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-364200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-485500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-570400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-481900</v>
       </c>
-      <c r="K91" s="3"/>
-    </row>
-    <row r="92" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="M91" s="3"/>
+    </row>
+    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -2755,9 +3201,15 @@
       <c r="J92" s="3">
         <v>0</v>
       </c>
-      <c r="K92" s="3"/>
-    </row>
-    <row r="93" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K92" s="3">
+        <v>0</v>
+      </c>
+      <c r="L92" s="3">
+        <v>0</v>
+      </c>
+      <c r="M92" s="3"/>
+    </row>
+    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -2782,36 +3234,48 @@
       <c r="J93" s="3">
         <v>0</v>
       </c>
-      <c r="K93" s="3"/>
-    </row>
-    <row r="94" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K93" s="3">
+        <v>0</v>
+      </c>
+      <c r="L93" s="3">
+        <v>0</v>
+      </c>
+      <c r="M93" s="3"/>
+    </row>
+    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-137200</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-1879400</v>
+      </c>
+      <c r="F94" s="3">
         <v>1668000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-2249800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-813600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>222500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>1588000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>317100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-2271600</v>
       </c>
-      <c r="K94" s="3"/>
-    </row>
-    <row r="95" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="M94" s="3"/>
+    </row>
+    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -2823,35 +3287,43 @@
       <c r="I95" s="3"/>
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
-    </row>
-    <row r="96" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L95" s="3"/>
+      <c r="M95" s="3"/>
+    </row>
+    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>591300</v>
+      </c>
+      <c r="E96" s="3">
+        <v>590400</v>
+      </c>
+      <c r="F96" s="3">
         <v>2062000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="G96" s="3">
         <v>528100</v>
       </c>
-      <c r="F96" s="3">
+      <c r="H96" s="3">
         <v>385200</v>
       </c>
-      <c r="G96" s="3">
+      <c r="I96" s="3">
         <v>455200</v>
       </c>
-      <c r="H96" s="3">
+      <c r="J96" s="3">
         <v>607300</v>
       </c>
-      <c r="I96" s="3">
+      <c r="K96" s="3">
         <v>441000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="L96" s="3">
         <v>404200</v>
       </c>
-      <c r="K96" s="3"/>
-    </row>
-    <row r="97" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="M96" s="3"/>
+    </row>
+    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -2876,9 +3348,15 @@
       <c r="J97" s="3">
         <v>0</v>
       </c>
-      <c r="K97" s="3"/>
-    </row>
-    <row r="98" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K97" s="3">
+        <v>0</v>
+      </c>
+      <c r="L97" s="3">
+        <v>0</v>
+      </c>
+      <c r="M97" s="3"/>
+    </row>
+    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -2903,9 +3381,15 @@
       <c r="J98" s="3">
         <v>0</v>
       </c>
-      <c r="K98" s="3"/>
-    </row>
-    <row r="99" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K98" s="3">
+        <v>0</v>
+      </c>
+      <c r="L98" s="3">
+        <v>0</v>
+      </c>
+      <c r="M98" s="3"/>
+    </row>
+    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -2930,88 +3414,112 @@
       <c r="J99" s="3">
         <v>0</v>
       </c>
-      <c r="K99" s="3"/>
-    </row>
-    <row r="100" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K99" s="3">
+        <v>0</v>
+      </c>
+      <c r="L99" s="3">
+        <v>0</v>
+      </c>
+      <c r="M99" s="3"/>
+    </row>
+    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1664000</v>
+      </c>
+      <c r="E100" s="3">
+        <v>1624800</v>
+      </c>
+      <c r="F100" s="3">
         <v>-2781200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-179800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-1582800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-733600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-1354700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-1860200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>178000</v>
       </c>
-      <c r="K100" s="3"/>
-    </row>
-    <row r="101" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="M100" s="3"/>
+    </row>
+    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>78900</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-63200</v>
+      </c>
+      <c r="F101" s="3">
         <v>-18900</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>-124800</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>39400</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>53500</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>-17700</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>-25500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>33100</v>
       </c>
-      <c r="K101" s="3"/>
-    </row>
-    <row r="102" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="M101" s="3"/>
+    </row>
+    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>147100</v>
+      </c>
+      <c r="E102" s="3">
+        <v>1028600</v>
+      </c>
+      <c r="F102" s="3">
         <v>137400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-1508300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-861000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>1020300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>1568900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>402400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-63900</v>
       </c>
-      <c r="K102" s="3"/>
+      <c r="M102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
